--- a/ALGS.xlsx
+++ b/ALGS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D70FBC9-1C70-4333-B881-ADC845592F57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DBD9AD0-F49C-49BD-A3AF-C5F68EC8D9E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16630" yWindow="2950" windowWidth="20840" windowHeight="16550" xr2:uid="{671139F4-5A1C-478A-811D-8EB628C88DE1}"/>
+    <workbookView xWindow="12920" yWindow="2910" windowWidth="22360" windowHeight="16580" xr2:uid="{671139F4-5A1C-478A-811D-8EB628C88DE1}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
   <si>
     <t>Price</t>
   </si>
@@ -64,9 +64,6 @@
     <t>ALG-055009</t>
   </si>
   <si>
-    <t>Q324</t>
-  </si>
-  <si>
     <t>ALG-000184</t>
   </si>
   <si>
@@ -82,9 +79,6 @@
     <t>II</t>
   </si>
   <si>
-    <t>THR-beta agonist</t>
-  </si>
-  <si>
     <t>MASH</t>
   </si>
   <si>
@@ -119,6 +113,12 @@
   </si>
   <si>
     <t>Week 12 reduction up to 46.2% by MRI-PDFF</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>pevifoscorvir</t>
   </si>
 </sst>
 </file>
@@ -270,12 +270,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -636,177 +635,139 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="10" t="s">
+      <c r="C2" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="11"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="10"/>
       <c r="K2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="L2" s="2">
-        <v>26.71</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="5"/>
+      <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="4"/>
       <c r="K3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="L3" s="13">
-        <v>6.2720000000000002</v>
-      </c>
-      <c r="M3" s="12" t="s">
-        <v>8</v>
+      <c r="L3" s="12">
+        <f>6.188223+4.217432</f>
+        <v>10.405654999999999</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="5"/>
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="4"/>
       <c r="K4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="L4" s="13">
+      <c r="L4" s="12">
         <f>+L2*L3</f>
-        <v>167.52512000000002</v>
+        <v>61.49742105</v>
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="5"/>
+      <c r="I5" s="4"/>
       <c r="K5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L5" s="13">
-        <v>74.900000000000006</v>
-      </c>
-      <c r="M5" s="12" t="s">
-        <v>8</v>
+      <c r="L5" s="12">
+        <f>29.98+24.929</f>
+        <v>54.908999999999999</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="5"/>
+      <c r="B6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="4"/>
       <c r="K6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L6" s="13">
+      <c r="L6" s="12">
         <v>0</v>
       </c>
-      <c r="M6" s="12" t="s">
-        <v>8</v>
+      <c r="M6" s="11" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="5"/>
+      <c r="I7" s="4"/>
       <c r="K7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L7" s="13">
+      <c r="L7" s="12">
         <f>+L4-L5+L6</f>
-        <v>92.62512000000001</v>
+        <v>6.5884210500000009</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" s="3"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="5"/>
+      <c r="I8" s="4"/>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="5"/>
+      <c r="I9" s="4"/>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="5"/>
+      <c r="I10" s="4"/>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B11" s="6"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="8"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -838,13 +799,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
-        <v>20</v>
+      <c r="A1" s="13" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -852,38 +813,38 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="13" x14ac:dyDescent="0.3">
-      <c r="C7" s="15" t="s">
-        <v>25</v>
+      <c r="C7" s="14" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C8" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
